--- a/tool/tblMedicalRecord_200rows.xlsx
+++ b/tool/tblMedicalRecord_200rows.xlsx
@@ -1657,8 +1657,10 @@
       <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BN001</t>
+        </is>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1683,8 +1685,10 @@
       <c r="B3">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BN002</t>
+        </is>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1709,8 +1713,10 @@
       <c r="B4">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BN003</t>
+        </is>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1735,8 +1741,10 @@
       <c r="B5">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BN004</t>
+        </is>
       </c>
       <c r="D5" t="s">
         <v>21</v>
@@ -1761,8 +1769,10 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BN005</t>
+        </is>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -1787,8 +1797,10 @@
       <c r="B7">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BN006</t>
+        </is>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -1813,8 +1825,10 @@
       <c r="B8">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
-        <v>31</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BN007</t>
+        </is>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -1839,8 +1853,10 @@
       <c r="B9">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
-        <v>35</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BN008</t>
+        </is>
       </c>
       <c r="D9" t="s">
         <v>36</v>
@@ -1865,8 +1881,10 @@
       <c r="B10">
         <v>74</v>
       </c>
-      <c r="C10" t="s">
-        <v>38</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BN009</t>
+        </is>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1891,8 +1909,10 @@
       <c r="B11">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>40</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BN010</t>
+        </is>
       </c>
       <c r="D11" t="s">
         <v>41</v>
@@ -1917,8 +1937,10 @@
       <c r="B12">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BN011</t>
+        </is>
       </c>
       <c r="D12" t="s">
         <v>44</v>
@@ -1943,8 +1965,10 @@
       <c r="B13">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
-        <v>45</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BN012</t>
+        </is>
       </c>
       <c r="D13" t="s">
         <v>46</v>
@@ -1969,8 +1993,10 @@
       <c r="B14">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>49</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BN013</t>
+        </is>
       </c>
       <c r="D14" t="s">
         <v>50</v>
@@ -1995,8 +2021,10 @@
       <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
-        <v>52</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BN014</t>
+        </is>
       </c>
       <c r="D15" t="s">
         <v>53</v>
@@ -2021,8 +2049,10 @@
       <c r="B16">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
-        <v>56</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BN015</t>
+        </is>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -2047,8 +2077,10 @@
       <c r="B17">
         <v>34</v>
       </c>
-      <c r="C17" t="s">
-        <v>58</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BN016</t>
+        </is>
       </c>
       <c r="D17" t="s">
         <v>59</v>
@@ -2073,8 +2105,10 @@
       <c r="B18">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
-        <v>60</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BN017</t>
+        </is>
       </c>
       <c r="D18" t="s">
         <v>61</v>
@@ -2099,8 +2133,10 @@
       <c r="B19">
         <v>64</v>
       </c>
-      <c r="C19" t="s">
-        <v>63</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BN018</t>
+        </is>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -2125,8 +2161,10 @@
       <c r="B20">
         <v>55</v>
       </c>
-      <c r="C20" t="s">
-        <v>60</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BN019</t>
+        </is>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -2151,8 +2189,10 @@
       <c r="B21">
         <v>68</v>
       </c>
-      <c r="C21" t="s">
-        <v>66</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BN020</t>
+        </is>
       </c>
       <c r="D21" t="s">
         <v>67</v>
@@ -2177,8 +2217,10 @@
       <c r="B22">
         <v>35</v>
       </c>
-      <c r="C22" t="s">
-        <v>49</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BN021</t>
+        </is>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -2203,8 +2245,10 @@
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" t="s">
-        <v>24</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BN022</t>
+        </is>
       </c>
       <c r="D23" t="s">
         <v>69</v>
@@ -2229,8 +2273,10 @@
       <c r="B24">
         <v>65</v>
       </c>
-      <c r="C24" t="s">
-        <v>70</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BN023</t>
+        </is>
       </c>
       <c r="D24" t="s">
         <v>71</v>
@@ -2255,8 +2301,10 @@
       <c r="B25">
         <v>68</v>
       </c>
-      <c r="C25" t="s">
-        <v>66</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BN024</t>
+        </is>
       </c>
       <c r="D25" t="s">
         <v>72</v>
@@ -2281,8 +2329,10 @@
       <c r="B26">
         <v>47</v>
       </c>
-      <c r="C26" t="s">
-        <v>43</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BN025</t>
+        </is>
       </c>
       <c r="D26" t="s">
         <v>73</v>
@@ -2307,8 +2357,10 @@
       <c r="B27">
         <v>11</v>
       </c>
-      <c r="C27" t="s">
-        <v>40</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BN026</t>
+        </is>
       </c>
       <c r="D27" t="s">
         <v>74</v>
@@ -2333,8 +2385,10 @@
       <c r="B28">
         <v>61</v>
       </c>
-      <c r="C28" t="s">
-        <v>75</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BN027</t>
+        </is>
       </c>
       <c r="D28" t="s">
         <v>76</v>
@@ -2359,8 +2413,10 @@
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29" t="s">
-        <v>27</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BN028</t>
+        </is>
       </c>
       <c r="D29" t="s">
         <v>77</v>
@@ -2385,8 +2441,10 @@
       <c r="B30">
         <v>48</v>
       </c>
-      <c r="C30" t="s">
-        <v>79</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BN029</t>
+        </is>
       </c>
       <c r="D30" t="s">
         <v>80</v>
@@ -2411,8 +2469,10 @@
       <c r="B31">
         <v>29</v>
       </c>
-      <c r="C31" t="s">
-        <v>81</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BN030</t>
+        </is>
       </c>
       <c r="D31" t="s">
         <v>82</v>
@@ -2437,8 +2497,10 @@
       <c r="B32">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
-        <v>83</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BN031</t>
+        </is>
       </c>
       <c r="D32" t="s">
         <v>84</v>
@@ -2463,8 +2525,10 @@
       <c r="B33">
         <v>9</v>
       </c>
-      <c r="C33" t="s">
-        <v>85</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BN032</t>
+        </is>
       </c>
       <c r="D33" t="s">
         <v>86</v>
@@ -2489,8 +2553,10 @@
       <c r="B34">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
-        <v>88</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BN033</t>
+        </is>
       </c>
       <c r="D34" t="s">
         <v>89</v>
@@ -2515,8 +2581,10 @@
       <c r="B35">
         <v>61</v>
       </c>
-      <c r="C35" t="s">
-        <v>75</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BN034</t>
+        </is>
       </c>
       <c r="D35" t="s">
         <v>90</v>
@@ -2541,8 +2609,10 @@
       <c r="B36">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
-        <v>91</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BN035</t>
+        </is>
       </c>
       <c r="D36" t="s">
         <v>92</v>
@@ -2567,8 +2637,10 @@
       <c r="B37">
         <v>13</v>
       </c>
-      <c r="C37" t="s">
-        <v>91</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BN036</t>
+        </is>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -2593,8 +2665,10 @@
       <c r="B38">
         <v>25</v>
       </c>
-      <c r="C38" t="s">
-        <v>94</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BN037</t>
+        </is>
       </c>
       <c r="D38" t="s">
         <v>95</v>
@@ -2619,8 +2693,10 @@
       <c r="B39">
         <v>60</v>
       </c>
-      <c r="C39" t="s">
-        <v>96</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BN038</t>
+        </is>
       </c>
       <c r="D39" t="s">
         <v>41</v>
@@ -2645,8 +2721,10 @@
       <c r="B40">
         <v>7</v>
       </c>
-      <c r="C40" t="s">
-        <v>97</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BN039</t>
+        </is>
       </c>
       <c r="D40" t="s">
         <v>98</v>
@@ -2671,8 +2749,10 @@
       <c r="B41">
         <v>53</v>
       </c>
-      <c r="C41" t="s">
-        <v>99</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BN040</t>
+        </is>
       </c>
       <c r="D41" t="s">
         <v>100</v>
@@ -2697,8 +2777,10 @@
       <c r="B42">
         <v>49</v>
       </c>
-      <c r="C42" t="s">
-        <v>35</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BN041</t>
+        </is>
       </c>
       <c r="D42" t="s">
         <v>93</v>
@@ -2723,8 +2805,10 @@
       <c r="B43">
         <v>72</v>
       </c>
-      <c r="C43" t="s">
-        <v>101</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BN042</t>
+        </is>
       </c>
       <c r="D43" t="s">
         <v>102</v>
@@ -2749,8 +2833,10 @@
       <c r="B44">
         <v>75</v>
       </c>
-      <c r="C44" t="s">
-        <v>103</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BN043</t>
+        </is>
       </c>
       <c r="D44" t="s">
         <v>104</v>
@@ -2775,8 +2861,10 @@
       <c r="B45">
         <v>62</v>
       </c>
-      <c r="C45" t="s">
-        <v>105</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BN044</t>
+        </is>
       </c>
       <c r="D45" t="s">
         <v>106</v>
@@ -2801,8 +2889,10 @@
       <c r="B46">
         <v>11</v>
       </c>
-      <c r="C46" t="s">
-        <v>40</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BN045</t>
+        </is>
       </c>
       <c r="D46" t="s">
         <v>107</v>
@@ -2827,8 +2917,10 @@
       <c r="B47">
         <v>16</v>
       </c>
-      <c r="C47" t="s">
-        <v>108</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BN046</t>
+        </is>
       </c>
       <c r="D47" t="s">
         <v>109</v>
@@ -2853,8 +2945,10 @@
       <c r="B48">
         <v>11</v>
       </c>
-      <c r="C48" t="s">
-        <v>40</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BN047</t>
+        </is>
       </c>
       <c r="D48" t="s">
         <v>110</v>
@@ -2879,8 +2973,10 @@
       <c r="B49">
         <v>34</v>
       </c>
-      <c r="C49" t="s">
-        <v>58</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BN048</t>
+        </is>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2905,8 +3001,10 @@
       <c r="B50">
         <v>17</v>
       </c>
-      <c r="C50" t="s">
-        <v>112</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BN049</t>
+        </is>
       </c>
       <c r="D50" t="s">
         <v>113</v>
@@ -2931,8 +3029,10 @@
       <c r="B51">
         <v>80</v>
       </c>
-      <c r="C51" t="s">
-        <v>114</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BN050</t>
+        </is>
       </c>
       <c r="D51" t="s">
         <v>115</v>
@@ -2957,8 +3057,10 @@
       <c r="B52">
         <v>34</v>
       </c>
-      <c r="C52" t="s">
-        <v>58</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BN051</t>
+        </is>
       </c>
       <c r="D52" t="s">
         <v>116</v>
@@ -2983,8 +3085,10 @@
       <c r="B53">
         <v>37</v>
       </c>
-      <c r="C53" t="s">
-        <v>117</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BN052</t>
+        </is>
       </c>
       <c r="D53" t="s">
         <v>118</v>
@@ -3009,8 +3113,10 @@
       <c r="B54">
         <v>2</v>
       </c>
-      <c r="C54" t="s">
-        <v>119</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BN053</t>
+        </is>
       </c>
       <c r="D54" t="s">
         <v>120</v>
@@ -3035,8 +3141,10 @@
       <c r="B55">
         <v>15</v>
       </c>
-      <c r="C55" t="s">
-        <v>8</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BN054</t>
+        </is>
       </c>
       <c r="D55" t="s">
         <v>121</v>
@@ -3061,8 +3169,10 @@
       <c r="B56">
         <v>78</v>
       </c>
-      <c r="C56" t="s">
-        <v>45</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BN055</t>
+        </is>
       </c>
       <c r="D56" t="s">
         <v>39</v>
@@ -3087,8 +3197,10 @@
       <c r="B57">
         <v>63</v>
       </c>
-      <c r="C57" t="s">
-        <v>122</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BN056</t>
+        </is>
       </c>
       <c r="D57" t="s">
         <v>123</v>
@@ -3113,8 +3225,10 @@
       <c r="B58">
         <v>6</v>
       </c>
-      <c r="C58" t="s">
-        <v>125</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BN057</t>
+        </is>
       </c>
       <c r="D58" t="s">
         <v>126</v>
@@ -3139,8 +3253,10 @@
       <c r="B59">
         <v>57</v>
       </c>
-      <c r="C59" t="s">
-        <v>127</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BN058</t>
+        </is>
       </c>
       <c r="D59" t="s">
         <v>128</v>
@@ -3165,8 +3281,10 @@
       <c r="B60">
         <v>10</v>
       </c>
-      <c r="C60" t="s">
-        <v>129</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BN059</t>
+        </is>
       </c>
       <c r="D60" t="s">
         <v>46</v>
@@ -3191,8 +3309,10 @@
       <c r="B61">
         <v>19</v>
       </c>
-      <c r="C61" t="s">
-        <v>130</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BN060</t>
+        </is>
       </c>
       <c r="D61" t="s">
         <v>131</v>
@@ -3217,8 +3337,10 @@
       <c r="B62">
         <v>46</v>
       </c>
-      <c r="C62" t="s">
-        <v>133</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BN061</t>
+        </is>
       </c>
       <c r="D62" t="s">
         <v>111</v>
@@ -3243,8 +3365,10 @@
       <c r="B63">
         <v>72</v>
       </c>
-      <c r="C63" t="s">
-        <v>101</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BN062</t>
+        </is>
       </c>
       <c r="D63" t="s">
         <v>134</v>
@@ -3269,8 +3393,10 @@
       <c r="B64">
         <v>53</v>
       </c>
-      <c r="C64" t="s">
-        <v>99</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BN063</t>
+        </is>
       </c>
       <c r="D64" t="s">
         <v>135</v>
@@ -3295,8 +3421,10 @@
       <c r="B65">
         <v>21</v>
       </c>
-      <c r="C65" t="s">
-        <v>136</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BN064</t>
+        </is>
       </c>
       <c r="D65" t="s">
         <v>137</v>
@@ -3321,8 +3449,10 @@
       <c r="B66">
         <v>59</v>
       </c>
-      <c r="C66" t="s">
-        <v>138</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BN065</t>
+        </is>
       </c>
       <c r="D66" t="s">
         <v>139</v>
@@ -3347,8 +3477,10 @@
       <c r="B67">
         <v>52</v>
       </c>
-      <c r="C67" t="s">
-        <v>140</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BN066</t>
+        </is>
       </c>
       <c r="D67" t="s">
         <v>141</v>
@@ -3373,8 +3505,10 @@
       <c r="B68">
         <v>52</v>
       </c>
-      <c r="C68" t="s">
-        <v>140</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BN067</t>
+        </is>
       </c>
       <c r="D68" t="s">
         <v>142</v>
@@ -3399,8 +3533,10 @@
       <c r="B69">
         <v>75</v>
       </c>
-      <c r="C69" t="s">
-        <v>103</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BN068</t>
+        </is>
       </c>
       <c r="D69" t="s">
         <v>143</v>
@@ -3425,8 +3561,10 @@
       <c r="B70">
         <v>41</v>
       </c>
-      <c r="C70" t="s">
-        <v>56</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BN069</t>
+        </is>
       </c>
       <c r="D70" t="s">
         <v>134</v>
@@ -3451,8 +3589,10 @@
       <c r="B71">
         <v>25</v>
       </c>
-      <c r="C71" t="s">
-        <v>94</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BN070</t>
+        </is>
       </c>
       <c r="D71" t="s">
         <v>143</v>
@@ -3477,8 +3617,10 @@
       <c r="B72">
         <v>69</v>
       </c>
-      <c r="C72" t="s">
-        <v>145</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BN071</t>
+        </is>
       </c>
       <c r="D72" t="s">
         <v>146</v>
@@ -3503,8 +3645,10 @@
       <c r="B73">
         <v>41</v>
       </c>
-      <c r="C73" t="s">
-        <v>56</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BN072</t>
+        </is>
       </c>
       <c r="D73" t="s">
         <v>121</v>
@@ -3529,8 +3673,10 @@
       <c r="B74">
         <v>42</v>
       </c>
-      <c r="C74" t="s">
-        <v>148</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BN073</t>
+        </is>
       </c>
       <c r="D74" t="s">
         <v>149</v>
@@ -3555,8 +3701,10 @@
       <c r="B75">
         <v>54</v>
       </c>
-      <c r="C75" t="s">
-        <v>150</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BN074</t>
+        </is>
       </c>
       <c r="D75" t="s">
         <v>110</v>
@@ -3581,8 +3729,10 @@
       <c r="B76">
         <v>52</v>
       </c>
-      <c r="C76" t="s">
-        <v>140</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BN075</t>
+        </is>
       </c>
       <c r="D76" t="s">
         <v>98</v>
@@ -3607,8 +3757,10 @@
       <c r="B77">
         <v>56</v>
       </c>
-      <c r="C77" t="s">
-        <v>151</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BN076</t>
+        </is>
       </c>
       <c r="D77" t="s">
         <v>152</v>
@@ -3633,8 +3785,10 @@
       <c r="B78">
         <v>57</v>
       </c>
-      <c r="C78" t="s">
-        <v>127</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BN077</t>
+        </is>
       </c>
       <c r="D78" t="s">
         <v>153</v>
@@ -3659,8 +3813,10 @@
       <c r="B79">
         <v>66</v>
       </c>
-      <c r="C79" t="s">
-        <v>155</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BN078</t>
+        </is>
       </c>
       <c r="D79" t="s">
         <v>156</v>
@@ -3685,8 +3841,10 @@
       <c r="B80">
         <v>26</v>
       </c>
-      <c r="C80" t="s">
-        <v>20</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BN079</t>
+        </is>
       </c>
       <c r="D80" t="s">
         <v>157</v>
@@ -3711,8 +3869,10 @@
       <c r="B81">
         <v>10</v>
       </c>
-      <c r="C81" t="s">
-        <v>129</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BN080</t>
+        </is>
       </c>
       <c r="D81" t="s">
         <v>159</v>
@@ -3737,8 +3897,10 @@
       <c r="B82">
         <v>64</v>
       </c>
-      <c r="C82" t="s">
-        <v>63</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BN081</t>
+        </is>
       </c>
       <c r="D82" t="s">
         <v>160</v>
@@ -3763,8 +3925,10 @@
       <c r="B83">
         <v>55</v>
       </c>
-      <c r="C83" t="s">
-        <v>60</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BN082</t>
+        </is>
       </c>
       <c r="D83" t="s">
         <v>161</v>
@@ -3789,8 +3953,10 @@
       <c r="B84">
         <v>72</v>
       </c>
-      <c r="C84" t="s">
-        <v>101</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BN083</t>
+        </is>
       </c>
       <c r="D84" t="s">
         <v>162</v>
@@ -3815,8 +3981,10 @@
       <c r="B85">
         <v>68</v>
       </c>
-      <c r="C85" t="s">
-        <v>66</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BN084</t>
+        </is>
       </c>
       <c r="D85" t="s">
         <v>163</v>
@@ -3841,8 +4009,10 @@
       <c r="B86">
         <v>55</v>
       </c>
-      <c r="C86" t="s">
-        <v>60</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BN085</t>
+        </is>
       </c>
       <c r="D86" t="s">
         <v>95</v>
@@ -3867,8 +4037,10 @@
       <c r="B87">
         <v>32</v>
       </c>
-      <c r="C87" t="s">
-        <v>164</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BN086</t>
+        </is>
       </c>
       <c r="D87" t="s">
         <v>165</v>
@@ -3893,8 +4065,10 @@
       <c r="B88">
         <v>57</v>
       </c>
-      <c r="C88" t="s">
-        <v>127</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BN087</t>
+        </is>
       </c>
       <c r="D88" t="s">
         <v>166</v>
@@ -3919,8 +4093,10 @@
       <c r="B89">
         <v>41</v>
       </c>
-      <c r="C89" t="s">
-        <v>56</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BN088</t>
+        </is>
       </c>
       <c r="D89" t="s">
         <v>13</v>
@@ -3945,8 +4121,10 @@
       <c r="B90">
         <v>20</v>
       </c>
-      <c r="C90" t="s">
-        <v>167</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BN089</t>
+        </is>
       </c>
       <c r="D90" t="s">
         <v>168</v>
@@ -3971,8 +4149,10 @@
       <c r="B91">
         <v>60</v>
       </c>
-      <c r="C91" t="s">
-        <v>96</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BN090</t>
+        </is>
       </c>
       <c r="D91" t="s">
         <v>169</v>
@@ -3997,8 +4177,10 @@
       <c r="B92">
         <v>3</v>
       </c>
-      <c r="C92" t="s">
-        <v>170</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BN091</t>
+        </is>
       </c>
       <c r="D92" t="s">
         <v>61</v>
@@ -4023,8 +4205,10 @@
       <c r="B93">
         <v>50</v>
       </c>
-      <c r="C93" t="s">
-        <v>171</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BN092</t>
+        </is>
       </c>
       <c r="D93" t="s">
         <v>172</v>
@@ -4049,8 +4233,10 @@
       <c r="B94">
         <v>29</v>
       </c>
-      <c r="C94" t="s">
-        <v>81</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BN093</t>
+        </is>
       </c>
       <c r="D94" t="s">
         <v>173</v>
@@ -4075,8 +4261,10 @@
       <c r="B95">
         <v>52</v>
       </c>
-      <c r="C95" t="s">
-        <v>140</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BN094</t>
+        </is>
       </c>
       <c r="D95" t="s">
         <v>174</v>
@@ -4101,8 +4289,10 @@
       <c r="B96">
         <v>4</v>
       </c>
-      <c r="C96" t="s">
-        <v>175</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BN095</t>
+        </is>
       </c>
       <c r="D96" t="s">
         <v>176</v>
@@ -4127,8 +4317,10 @@
       <c r="B97">
         <v>55</v>
       </c>
-      <c r="C97" t="s">
-        <v>60</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BN096</t>
+        </is>
       </c>
       <c r="D97" t="s">
         <v>177</v>
@@ -4153,8 +4345,10 @@
       <c r="B98">
         <v>49</v>
       </c>
-      <c r="C98" t="s">
-        <v>35</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BN097</t>
+        </is>
       </c>
       <c r="D98" t="s">
         <v>178</v>
@@ -4179,8 +4373,10 @@
       <c r="B99">
         <v>36</v>
       </c>
-      <c r="C99" t="s">
-        <v>88</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BN098</t>
+        </is>
       </c>
       <c r="D99" t="s">
         <v>179</v>
@@ -4205,8 +4401,10 @@
       <c r="B100">
         <v>7</v>
       </c>
-      <c r="C100" t="s">
-        <v>97</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BN099</t>
+        </is>
       </c>
       <c r="D100" t="s">
         <v>180</v>
@@ -4231,8 +4429,10 @@
       <c r="B101">
         <v>32</v>
       </c>
-      <c r="C101" t="s">
-        <v>164</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BN100</t>
+        </is>
       </c>
       <c r="D101" t="s">
         <v>181</v>
@@ -4257,8 +4457,10 @@
       <c r="B102">
         <v>17</v>
       </c>
-      <c r="C102" t="s">
-        <v>112</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BN101</t>
+        </is>
       </c>
       <c r="D102" t="s">
         <v>182</v>
@@ -4283,8 +4485,10 @@
       <c r="B103">
         <v>33</v>
       </c>
-      <c r="C103" t="s">
-        <v>183</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BN102</t>
+        </is>
       </c>
       <c r="D103" t="s">
         <v>184</v>
@@ -4309,8 +4513,10 @@
       <c r="B104">
         <v>40</v>
       </c>
-      <c r="C104" t="s">
-        <v>185</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BN103</t>
+        </is>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -4335,8 +4541,10 @@
       <c r="B105">
         <v>51</v>
       </c>
-      <c r="C105" t="s">
-        <v>187</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BN104</t>
+        </is>
       </c>
       <c r="D105" t="s">
         <v>168</v>
@@ -4361,8 +4569,10 @@
       <c r="B106">
         <v>39</v>
       </c>
-      <c r="C106" t="s">
-        <v>188</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BN105</t>
+        </is>
       </c>
       <c r="D106" t="s">
         <v>189</v>
@@ -4387,8 +4597,10 @@
       <c r="B107">
         <v>69</v>
       </c>
-      <c r="C107" t="s">
-        <v>145</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BN106</t>
+        </is>
       </c>
       <c r="D107" t="s">
         <v>110</v>
@@ -4413,8 +4625,10 @@
       <c r="B108">
         <v>2</v>
       </c>
-      <c r="C108" t="s">
-        <v>119</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BN107</t>
+        </is>
       </c>
       <c r="D108" t="s">
         <v>190</v>
@@ -4439,8 +4653,10 @@
       <c r="B109">
         <v>59</v>
       </c>
-      <c r="C109" t="s">
-        <v>138</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BN108</t>
+        </is>
       </c>
       <c r="D109" t="s">
         <v>191</v>
@@ -4465,8 +4681,10 @@
       <c r="B110">
         <v>69</v>
       </c>
-      <c r="C110" t="s">
-        <v>145</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BN109</t>
+        </is>
       </c>
       <c r="D110" t="s">
         <v>192</v>
@@ -4491,8 +4709,10 @@
       <c r="B111">
         <v>32</v>
       </c>
-      <c r="C111" t="s">
-        <v>164</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BN110</t>
+        </is>
       </c>
       <c r="D111" t="s">
         <v>193</v>
@@ -4517,8 +4737,10 @@
       <c r="B112">
         <v>79</v>
       </c>
-      <c r="C112" t="s">
-        <v>194</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BN111</t>
+        </is>
       </c>
       <c r="D112" t="s">
         <v>195</v>
@@ -4543,8 +4765,10 @@
       <c r="B113">
         <v>63</v>
       </c>
-      <c r="C113" t="s">
-        <v>122</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BN112</t>
+        </is>
       </c>
       <c r="D113" t="s">
         <v>146</v>
@@ -4569,8 +4793,10 @@
       <c r="B114">
         <v>36</v>
       </c>
-      <c r="C114" t="s">
-        <v>88</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BN113</t>
+        </is>
       </c>
       <c r="D114" t="s">
         <v>196</v>
@@ -4595,8 +4821,10 @@
       <c r="B115">
         <v>53</v>
       </c>
-      <c r="C115" t="s">
-        <v>99</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BN114</t>
+        </is>
       </c>
       <c r="D115" t="s">
         <v>197</v>
@@ -4621,8 +4849,10 @@
       <c r="B116">
         <v>3</v>
       </c>
-      <c r="C116" t="s">
-        <v>170</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BN115</t>
+        </is>
       </c>
       <c r="D116" t="s">
         <v>198</v>
@@ -4647,8 +4877,10 @@
       <c r="B117">
         <v>75</v>
       </c>
-      <c r="C117" t="s">
-        <v>103</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BN116</t>
+        </is>
       </c>
       <c r="D117" t="s">
         <v>199</v>
@@ -4673,8 +4905,10 @@
       <c r="B118">
         <v>71</v>
       </c>
-      <c r="C118" t="s">
-        <v>200</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BN117</t>
+        </is>
       </c>
       <c r="D118" t="s">
         <v>201</v>
@@ -4699,8 +4933,10 @@
       <c r="B119">
         <v>33</v>
       </c>
-      <c r="C119" t="s">
-        <v>183</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BN118</t>
+        </is>
       </c>
       <c r="D119" t="s">
         <v>202</v>
@@ -4725,8 +4961,10 @@
       <c r="B120">
         <v>24</v>
       </c>
-      <c r="C120" t="s">
-        <v>203</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BN119</t>
+        </is>
       </c>
       <c r="D120" t="s">
         <v>204</v>
@@ -4751,8 +4989,10 @@
       <c r="B121">
         <v>77</v>
       </c>
-      <c r="C121" t="s">
-        <v>205</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BN120</t>
+        </is>
       </c>
       <c r="D121" t="s">
         <v>206</v>
@@ -4777,8 +5017,10 @@
       <c r="B122">
         <v>23</v>
       </c>
-      <c r="C122" t="s">
-        <v>207</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BN121</t>
+        </is>
       </c>
       <c r="D122" t="s">
         <v>208</v>
@@ -4803,8 +5045,10 @@
       <c r="B123">
         <v>6</v>
       </c>
-      <c r="C123" t="s">
-        <v>125</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BN122</t>
+        </is>
       </c>
       <c r="D123" t="s">
         <v>209</v>
@@ -4829,8 +5073,10 @@
       <c r="B124">
         <v>2</v>
       </c>
-      <c r="C124" t="s">
-        <v>119</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BN123</t>
+        </is>
       </c>
       <c r="D124" t="s">
         <v>210</v>
@@ -4855,8 +5101,10 @@
       <c r="B125">
         <v>24</v>
       </c>
-      <c r="C125" t="s">
-        <v>203</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BN124</t>
+        </is>
       </c>
       <c r="D125" t="s">
         <v>211</v>
@@ -4881,8 +5129,10 @@
       <c r="B126">
         <v>63</v>
       </c>
-      <c r="C126" t="s">
-        <v>122</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BN125</t>
+        </is>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -4907,8 +5157,10 @@
       <c r="B127">
         <v>20</v>
       </c>
-      <c r="C127" t="s">
-        <v>167</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BN126</t>
+        </is>
       </c>
       <c r="D127" t="s">
         <v>210</v>
@@ -4933,8 +5185,10 @@
       <c r="B128">
         <v>54</v>
       </c>
-      <c r="C128" t="s">
-        <v>150</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BN127</t>
+        </is>
       </c>
       <c r="D128" t="s">
         <v>152</v>
@@ -4959,8 +5213,10 @@
       <c r="B129">
         <v>58</v>
       </c>
-      <c r="C129" t="s">
-        <v>212</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BN128</t>
+        </is>
       </c>
       <c r="D129" t="s">
         <v>213</v>
@@ -4985,8 +5241,10 @@
       <c r="B130">
         <v>80</v>
       </c>
-      <c r="C130" t="s">
-        <v>114</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BN129</t>
+        </is>
       </c>
       <c r="D130" t="s">
         <v>72</v>
@@ -5011,8 +5269,10 @@
       <c r="B131">
         <v>11</v>
       </c>
-      <c r="C131" t="s">
-        <v>40</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BN130</t>
+        </is>
       </c>
       <c r="D131" t="s">
         <v>59</v>
@@ -5037,8 +5297,10 @@
       <c r="B132">
         <v>1</v>
       </c>
-      <c r="C132" t="s">
-        <v>24</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BN131</t>
+        </is>
       </c>
       <c r="D132" t="s">
         <v>214</v>
@@ -5063,8 +5325,10 @@
       <c r="B133">
         <v>5</v>
       </c>
-      <c r="C133" t="s">
-        <v>52</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BN132</t>
+        </is>
       </c>
       <c r="D133" t="s">
         <v>215</v>
@@ -5089,8 +5353,10 @@
       <c r="B134">
         <v>30</v>
       </c>
-      <c r="C134" t="s">
-        <v>216</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BN133</t>
+        </is>
       </c>
       <c r="D134" t="s">
         <v>217</v>
@@ -5115,8 +5381,10 @@
       <c r="B135">
         <v>15</v>
       </c>
-      <c r="C135" t="s">
-        <v>8</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BN134</t>
+        </is>
       </c>
       <c r="D135" t="s">
         <v>50</v>
@@ -5141,8 +5409,10 @@
       <c r="B136">
         <v>10</v>
       </c>
-      <c r="C136" t="s">
-        <v>129</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BN135</t>
+        </is>
       </c>
       <c r="D136" t="s">
         <v>135</v>
@@ -5167,8 +5437,10 @@
       <c r="B137">
         <v>57</v>
       </c>
-      <c r="C137" t="s">
-        <v>127</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>BN136</t>
+        </is>
       </c>
       <c r="D137" t="s">
         <v>218</v>
@@ -5193,8 +5465,10 @@
       <c r="B138">
         <v>65</v>
       </c>
-      <c r="C138" t="s">
-        <v>70</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>BN137</t>
+        </is>
       </c>
       <c r="D138" t="s">
         <v>219</v>
@@ -5219,8 +5493,10 @@
       <c r="B139">
         <v>56</v>
       </c>
-      <c r="C139" t="s">
-        <v>151</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>BN138</t>
+        </is>
       </c>
       <c r="D139" t="s">
         <v>220</v>
@@ -5245,8 +5521,10 @@
       <c r="B140">
         <v>74</v>
       </c>
-      <c r="C140" t="s">
-        <v>38</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>BN139</t>
+        </is>
       </c>
       <c r="D140" t="s">
         <v>221</v>
@@ -5271,8 +5549,10 @@
       <c r="B141">
         <v>23</v>
       </c>
-      <c r="C141" t="s">
-        <v>207</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>BN140</t>
+        </is>
       </c>
       <c r="D141" t="s">
         <v>222</v>
@@ -5297,8 +5577,10 @@
       <c r="B142">
         <v>75</v>
       </c>
-      <c r="C142" t="s">
-        <v>103</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BN141</t>
+        </is>
       </c>
       <c r="D142" t="s">
         <v>223</v>
@@ -5323,8 +5605,10 @@
       <c r="B143">
         <v>53</v>
       </c>
-      <c r="C143" t="s">
-        <v>99</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>BN142</t>
+        </is>
       </c>
       <c r="D143" t="s">
         <v>224</v>
@@ -5349,8 +5633,10 @@
       <c r="B144">
         <v>53</v>
       </c>
-      <c r="C144" t="s">
-        <v>99</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BN143</t>
+        </is>
       </c>
       <c r="D144" t="s">
         <v>213</v>
@@ -5375,8 +5661,10 @@
       <c r="B145">
         <v>59</v>
       </c>
-      <c r="C145" t="s">
-        <v>138</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BN144</t>
+        </is>
       </c>
       <c r="D145" t="s">
         <v>82</v>
@@ -5401,8 +5689,10 @@
       <c r="B146">
         <v>66</v>
       </c>
-      <c r="C146" t="s">
-        <v>155</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>BN145</t>
+        </is>
       </c>
       <c r="D146" t="s">
         <v>225</v>
@@ -5427,8 +5717,10 @@
       <c r="B147">
         <v>25</v>
       </c>
-      <c r="C147" t="s">
-        <v>94</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BN146</t>
+        </is>
       </c>
       <c r="D147" t="s">
         <v>226</v>
@@ -5453,8 +5745,10 @@
       <c r="B148">
         <v>27</v>
       </c>
-      <c r="C148" t="s">
-        <v>227</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BN147</t>
+        </is>
       </c>
       <c r="D148" t="s">
         <v>67</v>
@@ -5479,8 +5773,10 @@
       <c r="B149">
         <v>16</v>
       </c>
-      <c r="C149" t="s">
-        <v>108</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BN148</t>
+        </is>
       </c>
       <c r="D149" t="s">
         <v>228</v>
@@ -5505,8 +5801,10 @@
       <c r="B150">
         <v>71</v>
       </c>
-      <c r="C150" t="s">
-        <v>200</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>BN149</t>
+        </is>
       </c>
       <c r="D150" t="s">
         <v>209</v>
@@ -5531,8 +5829,10 @@
       <c r="B151">
         <v>60</v>
       </c>
-      <c r="C151" t="s">
-        <v>96</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>BN150</t>
+        </is>
       </c>
       <c r="D151" t="s">
         <v>229</v>
@@ -5557,8 +5857,10 @@
       <c r="B152">
         <v>35</v>
       </c>
-      <c r="C152" t="s">
-        <v>49</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>BN151</t>
+        </is>
       </c>
       <c r="D152" t="s">
         <v>190</v>
@@ -5583,8 +5885,10 @@
       <c r="B153">
         <v>71</v>
       </c>
-      <c r="C153" t="s">
-        <v>200</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>BN152</t>
+        </is>
       </c>
       <c r="D153" t="s">
         <v>230</v>
@@ -5609,8 +5913,10 @@
       <c r="B154">
         <v>9</v>
       </c>
-      <c r="C154" t="s">
-        <v>85</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BN153</t>
+        </is>
       </c>
       <c r="D154" t="s">
         <v>165</v>
@@ -5635,8 +5941,10 @@
       <c r="B155">
         <v>1</v>
       </c>
-      <c r="C155" t="s">
-        <v>24</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BN154</t>
+        </is>
       </c>
       <c r="D155" t="s">
         <v>231</v>
@@ -5661,8 +5969,10 @@
       <c r="B156">
         <v>20</v>
       </c>
-      <c r="C156" t="s">
-        <v>167</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BN155</t>
+        </is>
       </c>
       <c r="D156" t="s">
         <v>197</v>
@@ -5687,8 +5997,10 @@
       <c r="B157">
         <v>70</v>
       </c>
-      <c r="C157" t="s">
-        <v>232</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BN156</t>
+        </is>
       </c>
       <c r="D157" t="s">
         <v>214</v>
@@ -5713,8 +6025,10 @@
       <c r="B158">
         <v>50</v>
       </c>
-      <c r="C158" t="s">
-        <v>171</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>BN157</t>
+        </is>
       </c>
       <c r="D158" t="s">
         <v>41</v>
@@ -5739,8 +6053,10 @@
       <c r="B159">
         <v>49</v>
       </c>
-      <c r="C159" t="s">
-        <v>35</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>BN158</t>
+        </is>
       </c>
       <c r="D159" t="s">
         <v>110</v>
@@ -5765,8 +6081,10 @@
       <c r="B160">
         <v>17</v>
       </c>
-      <c r="C160" t="s">
-        <v>112</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BN159</t>
+        </is>
       </c>
       <c r="D160" t="s">
         <v>233</v>
@@ -5791,8 +6109,10 @@
       <c r="B161">
         <v>68</v>
       </c>
-      <c r="C161" t="s">
-        <v>66</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BN160</t>
+        </is>
       </c>
       <c r="D161" t="s">
         <v>234</v>
@@ -5817,8 +6137,10 @@
       <c r="B162">
         <v>61</v>
       </c>
-      <c r="C162" t="s">
-        <v>75</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BN161</t>
+        </is>
       </c>
       <c r="D162" t="s">
         <v>235</v>
@@ -5843,8 +6165,10 @@
       <c r="B163">
         <v>69</v>
       </c>
-      <c r="C163" t="s">
-        <v>145</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BN162</t>
+        </is>
       </c>
       <c r="D163" t="s">
         <v>195</v>
@@ -5869,8 +6193,10 @@
       <c r="B164">
         <v>80</v>
       </c>
-      <c r="C164" t="s">
-        <v>114</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BN163</t>
+        </is>
       </c>
       <c r="D164" t="s">
         <v>236</v>
@@ -5895,8 +6221,10 @@
       <c r="B165">
         <v>12</v>
       </c>
-      <c r="C165" t="s">
-        <v>16</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BN164</t>
+        </is>
       </c>
       <c r="D165" t="s">
         <v>237</v>
@@ -5921,8 +6249,10 @@
       <c r="B166">
         <v>39</v>
       </c>
-      <c r="C166" t="s">
-        <v>188</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BN165</t>
+        </is>
       </c>
       <c r="D166" t="s">
         <v>238</v>
@@ -5947,8 +6277,10 @@
       <c r="B167">
         <v>48</v>
       </c>
-      <c r="C167" t="s">
-        <v>79</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BN166</t>
+        </is>
       </c>
       <c r="D167" t="s">
         <v>131</v>
@@ -5973,8 +6305,10 @@
       <c r="B168">
         <v>24</v>
       </c>
-      <c r="C168" t="s">
-        <v>203</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BN167</t>
+        </is>
       </c>
       <c r="D168" t="s">
         <v>239</v>
@@ -5999,8 +6333,10 @@
       <c r="B169">
         <v>31</v>
       </c>
-      <c r="C169" t="s">
-        <v>240</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BN168</t>
+        </is>
       </c>
       <c r="D169" t="s">
         <v>241</v>
@@ -6025,8 +6361,10 @@
       <c r="B170">
         <v>33</v>
       </c>
-      <c r="C170" t="s">
-        <v>183</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BN169</t>
+        </is>
       </c>
       <c r="D170" t="s">
         <v>242</v>
@@ -6051,8 +6389,10 @@
       <c r="B171">
         <v>70</v>
       </c>
-      <c r="C171" t="s">
-        <v>232</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BN170</t>
+        </is>
       </c>
       <c r="D171" t="s">
         <v>107</v>
@@ -6077,8 +6417,10 @@
       <c r="B172">
         <v>55</v>
       </c>
-      <c r="C172" t="s">
-        <v>60</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BN171</t>
+        </is>
       </c>
       <c r="D172" t="s">
         <v>113</v>
@@ -6103,8 +6445,10 @@
       <c r="B173">
         <v>14</v>
       </c>
-      <c r="C173" t="s">
-        <v>12</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BN172</t>
+        </is>
       </c>
       <c r="D173" t="s">
         <v>243</v>
@@ -6129,8 +6473,10 @@
       <c r="B174">
         <v>38</v>
       </c>
-      <c r="C174" t="s">
-        <v>244</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BN173</t>
+        </is>
       </c>
       <c r="D174" t="s">
         <v>245</v>
@@ -6155,8 +6501,10 @@
       <c r="B175">
         <v>73</v>
       </c>
-      <c r="C175" t="s">
-        <v>246</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BN174</t>
+        </is>
       </c>
       <c r="D175" t="s">
         <v>247</v>
@@ -6181,8 +6529,10 @@
       <c r="B176">
         <v>78</v>
       </c>
-      <c r="C176" t="s">
-        <v>45</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BN175</t>
+        </is>
       </c>
       <c r="D176" t="s">
         <v>180</v>
@@ -6207,8 +6557,10 @@
       <c r="B177">
         <v>18</v>
       </c>
-      <c r="C177" t="s">
-        <v>248</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BN176</t>
+        </is>
       </c>
       <c r="D177" t="s">
         <v>249</v>
@@ -6233,8 +6585,10 @@
       <c r="B178">
         <v>57</v>
       </c>
-      <c r="C178" t="s">
-        <v>127</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BN177</t>
+        </is>
       </c>
       <c r="D178" t="s">
         <v>250</v>
@@ -6259,8 +6613,10 @@
       <c r="B179">
         <v>42</v>
       </c>
-      <c r="C179" t="s">
-        <v>148</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BN178</t>
+        </is>
       </c>
       <c r="D179" t="s">
         <v>251</v>
@@ -6285,8 +6641,10 @@
       <c r="B180">
         <v>68</v>
       </c>
-      <c r="C180" t="s">
-        <v>66</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BN179</t>
+        </is>
       </c>
       <c r="D180" t="s">
         <v>106</v>
@@ -6311,8 +6669,10 @@
       <c r="B181">
         <v>38</v>
       </c>
-      <c r="C181" t="s">
-        <v>244</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BN180</t>
+        </is>
       </c>
       <c r="D181" t="s">
         <v>252</v>
@@ -6337,8 +6697,10 @@
       <c r="B182">
         <v>29</v>
       </c>
-      <c r="C182" t="s">
-        <v>81</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BN181</t>
+        </is>
       </c>
       <c r="D182" t="s">
         <v>253</v>
@@ -6363,8 +6725,10 @@
       <c r="B183">
         <v>2</v>
       </c>
-      <c r="C183" t="s">
-        <v>119</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BN182</t>
+        </is>
       </c>
       <c r="D183" t="s">
         <v>67</v>
@@ -6389,8 +6753,10 @@
       <c r="B184">
         <v>75</v>
       </c>
-      <c r="C184" t="s">
-        <v>103</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BN183</t>
+        </is>
       </c>
       <c r="D184" t="s">
         <v>190</v>
@@ -6415,8 +6781,10 @@
       <c r="B185">
         <v>61</v>
       </c>
-      <c r="C185" t="s">
-        <v>75</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BN184</t>
+        </is>
       </c>
       <c r="D185" t="s">
         <v>72</v>
@@ -6441,8 +6809,10 @@
       <c r="B186">
         <v>9</v>
       </c>
-      <c r="C186" t="s">
-        <v>85</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BN185</t>
+        </is>
       </c>
       <c r="D186" t="s">
         <v>241</v>
@@ -6467,8 +6837,10 @@
       <c r="B187">
         <v>18</v>
       </c>
-      <c r="C187" t="s">
-        <v>248</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BN186</t>
+        </is>
       </c>
       <c r="D187" t="s">
         <v>238</v>
@@ -6493,8 +6865,10 @@
       <c r="B188">
         <v>31</v>
       </c>
-      <c r="C188" t="s">
-        <v>240</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BN187</t>
+        </is>
       </c>
       <c r="D188" t="s">
         <v>254</v>
@@ -6519,8 +6893,10 @@
       <c r="B189">
         <v>54</v>
       </c>
-      <c r="C189" t="s">
-        <v>150</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BN188</t>
+        </is>
       </c>
       <c r="D189" t="s">
         <v>255</v>
@@ -6545,8 +6921,10 @@
       <c r="B190">
         <v>79</v>
       </c>
-      <c r="C190" t="s">
-        <v>194</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BN189</t>
+        </is>
       </c>
       <c r="D190" t="s">
         <v>179</v>
@@ -6571,8 +6949,10 @@
       <c r="B191">
         <v>57</v>
       </c>
-      <c r="C191" t="s">
-        <v>127</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BN190</t>
+        </is>
       </c>
       <c r="D191" t="s">
         <v>41</v>
@@ -6597,8 +6977,10 @@
       <c r="B192">
         <v>46</v>
       </c>
-      <c r="C192" t="s">
-        <v>133</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BN191</t>
+        </is>
       </c>
       <c r="D192" t="s">
         <v>93</v>
@@ -6623,8 +7005,10 @@
       <c r="B193">
         <v>12</v>
       </c>
-      <c r="C193" t="s">
-        <v>16</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BN192</t>
+        </is>
       </c>
       <c r="D193" t="s">
         <v>57</v>
@@ -6649,8 +7033,10 @@
       <c r="B194">
         <v>43</v>
       </c>
-      <c r="C194" t="s">
-        <v>256</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BN193</t>
+        </is>
       </c>
       <c r="D194" t="s">
         <v>257</v>
@@ -6675,8 +7061,10 @@
       <c r="B195">
         <v>27</v>
       </c>
-      <c r="C195" t="s">
-        <v>227</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BN194</t>
+        </is>
       </c>
       <c r="D195" t="s">
         <v>71</v>
@@ -6701,8 +7089,10 @@
       <c r="B196">
         <v>1</v>
       </c>
-      <c r="C196" t="s">
-        <v>24</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BN195</t>
+        </is>
       </c>
       <c r="D196" t="s">
         <v>258</v>
@@ -6727,8 +7117,10 @@
       <c r="B197">
         <v>23</v>
       </c>
-      <c r="C197" t="s">
-        <v>207</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BN196</t>
+        </is>
       </c>
       <c r="D197" t="s">
         <v>259</v>
@@ -6753,8 +7145,10 @@
       <c r="B198">
         <v>31</v>
       </c>
-      <c r="C198" t="s">
-        <v>240</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BN197</t>
+        </is>
       </c>
       <c r="D198" t="s">
         <v>156</v>
@@ -6779,8 +7173,10 @@
       <c r="B199">
         <v>17</v>
       </c>
-      <c r="C199" t="s">
-        <v>112</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BN198</t>
+        </is>
       </c>
       <c r="D199" t="s">
         <v>260</v>
@@ -6805,8 +7201,10 @@
       <c r="B200">
         <v>47</v>
       </c>
-      <c r="C200" t="s">
-        <v>43</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BN199</t>
+        </is>
       </c>
       <c r="D200" t="s">
         <v>233</v>
@@ -6831,8 +7229,10 @@
       <c r="B201">
         <v>79</v>
       </c>
-      <c r="C201" t="s">
-        <v>194</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BN200</t>
+        </is>
       </c>
       <c r="D201" t="s">
         <v>9</v>
